--- a/04_DESIGN_TABLES/DesignTable_2602.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2602.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -559,6 +559,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1911,24 +1916,59 @@
           <t>2602-08-08-08-FG</t>
         </is>
       </c>
+      <c r="B23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.7</v>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>2602-08-08-08-FG</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>3/4-16 x 3/4-16 (JIC) x 1/2-14 (NPTF female branch)</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2602-08-08-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2602-08-08-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): M1_1@DRIVE: Brennan TFA catalog p.49 table TFA-p049-t02 "2602-FG MJ-MJ-FP TEE" row 2602-08-08-08-FG col "M1 LGTH" = "1.520" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 418.9, page verified True) [Brennan = yes 2026-10-18] - B1 JIC run leg (column mapping: REPORT.md, table 2602); = OMi WebsitePartsInfo2026 Items!N815 "M 1 Size" = 1.520 (same value; OMi and Brennan count as one source); M1_2@DRIVE: Brennan TFA catalog p.49 table TFA-p049-t02 "2602-FG MJ-MJ-FP TEE" row 2602-08-08-08-FG col "M2 LGTH" = "1.520" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 418.9, page verified True) [Brennan = yes 2026-10-18] - B2 JIC run leg (column mapping: REPORT.md, table 2602); = OMi WebsitePartsInfo2026 Items!O815 "M 2 Size" = 1.520 (same value; OMi and Brennan count as one source); N1@DRIVE: Brennan TFA catalog p.49 table TFA-p049-t02 "2602-FG MJ-MJ-FP TEE" row 2602-08-08-08-FG col "N LGTH" = "1.230" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 418.9, page verified True) [Brennan = yes 2026-10-18] - run axis to the female NPTF branch port face (column mapping: REPORT.md, table 2602); = OMi WebsitePartsInfo2026 Items!P815 "L 1 Size" = 1.230 (same value; OMi and Brennan count as one source); Y1@DRIVE: Brennan TFA catalog p.49 table TFA-p049-t02 "2602-FG MJ-MJ-FP TEE" row 2602-08-08-08-FG col "Y FLATS" = "1.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 418.9, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 2602); = OMi WebsitePartsInfo2026 Items!R815 "Hex Flat" = 1.062 (same value; OMi and Brennan count as one source); D1@BORE: Brennan TFA catalog p.49 table TFA-p049-t02 "2602-FG MJ-MJ-FP TEE" row 2602-08-08-08-FG col "B1 DRILL" = "0.391" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 418.9, page verified True) [Brennan = yes 2026-10-18] - B1 JIC drill (column mapping: REPORT.md, table 2602); = OMi WebsitePartsInfo2026 Items!S815 "Side 1 ID" = 0.391 (same value; OMi and Brennan count as one source); D2@BORE: Brennan TFA catalog p.49 table TFA-p049-t02 "2602-FG MJ-MJ-FP TEE" row 2602-08-08-08-FG col "B2 DRILL" = "0.391" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 418.9, page verified True) [Brennan = yes 2026-10-18] - B2 JIC drill (column mapping: REPORT.md, table 2602); = OMi WebsitePartsInfo2026 Items!X815 "Side 2 ID" = 0.391 (same value; OMi and Brennan count as one source); TAPDRILL@BORE: end library: tap drill of the -08 female NPTF port = 0.7 (gen_straight2 FPT[8] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-TRANSFER-TAPDRILL = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; THDMAJ_B1@DRIVE: end library: male JIC -08 thread major = 0.75 (gen_straight2 JIC[8] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B2@DRIVE: end library: male JIC -08 thread major = 0.75 (gen_straight2 JIC[8] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A@DRIVE: end library: pipe OD of the -08 NPTF thread = 0.84 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[8], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p049-t02 thread columns (B1 SAE 37Deg 3/4-16, B2 SAE 37Deg 3/4-16, A3 NPTF 1/2-14) and OMi Items Side 1 / 2 / 3 Thread</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2602-08-08-08 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2602-08-08-08 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog (= OMi Items, one source), end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -1939,6 +1979,11 @@
       <c r="R23" t="inlineStr">
         <is>
           <t>2602-08-08-08-FG</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
